--- a/excel-files/MANILA/FLORENTINO TORRES HIGH SCHOOL.xlsx
+++ b/excel-files/MANILA/FLORENTINO TORRES HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53C174A4-EC58-4EBE-A449-7E3D6E8A98A8}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFA99A83-EC9B-486A-BFEC-4F5A331EFB60}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5433,8 +5433,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E91:E98 E51:E59 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E61:E69" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -13535,12 +13535,6 @@
     </row>
     <row r="144" spans="10:10">
       <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
         <f>#REF!*8</f>
         <v>#REF!</v>
       </c>
